--- a/Result/profitability/6237.xlsx
+++ b/Result/profitability/6237.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.61</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1800000000000001</v>
+        <v>-0.1325000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>51.61125</v>
+        <v>49.60125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.76</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01375000000000012</v>
+        <v>-0.07375000000000012</v>
       </c>
       <c r="N3" t="n">
-        <v>55.29</v>
+        <v>52.93875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.72</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03999999999999988</v>
+        <v>0.07999999999999988</v>
       </c>
       <c r="N4" t="n">
-        <v>57.89749999999999</v>
+        <v>57.72499999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.48</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04374999999999987</v>
+        <v>0.1162499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>60.40125</v>
+        <v>59.89125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.65</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2212499999999999</v>
+        <v>0.2199999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>64.875</v>
+        <v>64.36499999999999</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-1.37</v>
       </c>
       <c r="M7" t="n">
-        <v>0.07249999999999987</v>
+        <v>0.05749999999999986</v>
       </c>
       <c r="N7" t="n">
-        <v>69.61</v>
+        <v>68.96374999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.51</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1449999999999999</v>
+        <v>0.1512499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>73.41749999999999</v>
+        <v>73.35374999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,10 +1518,10 @@
         <v>0.44</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2299999999999999</v>
+        <v>0.2299999999999998</v>
       </c>
       <c r="N9" t="n">
-        <v>77.15624999999999</v>
+        <v>77.15625</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>-0.63</v>
       </c>
       <c r="M13" t="n">
-        <v>0.05124999999999988</v>
+        <v>0.05124999999999985</v>
       </c>
       <c r="N13" t="n">
         <v>77.48375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6237</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>170</v>
+      </c>
+      <c r="D75" t="n">
+        <v>102</v>
+      </c>
+      <c r="E75" t="n">
+        <v>68</v>
+      </c>
+      <c r="F75" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-6.27%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-15</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.2800000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>46.21375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.04999999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2083333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.509999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01260504201680668</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7532467532467533</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.079999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.09266409266409259</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
